--- a/input/mapping/036. OCB_GOLD_TCKH_V_TB_NIM_HOP.xlsx
+++ b/input/mapping/036. OCB_GOLD_TCKH_V_TB_NIM_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1581" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D44616-DD23-450E-A79B-2A606858BE1E}"/>
+  <xr:revisionPtr revIDLastSave="1583" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F2AE73C-7E6E-40D1-8ADB-2465594F7E76}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="8" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -4158,7 +4158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="320">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4676,186 +4676,297 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -4922,119 +5033,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
@@ -5422,49 +5420,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="204"/>
-      <c r="Y1" s="204"/>
-      <c r="Z1" s="204"/>
-      <c r="AA1" s="204"/>
-      <c r="AB1" s="204"/>
-      <c r="AC1" s="204"/>
-      <c r="AD1" s="204"/>
-      <c r="AE1" s="204"/>
-      <c r="AF1" s="204"/>
-      <c r="AG1" s="204"/>
-      <c r="AH1" s="204"/>
-      <c r="AI1" s="204"/>
-      <c r="AJ1" s="204"/>
-      <c r="AK1" s="204"/>
-      <c r="AL1" s="204"/>
-      <c r="AM1" s="204"/>
-      <c r="AN1" s="204"/>
-      <c r="AO1" s="204"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="235"/>
+      <c r="M1" s="235"/>
+      <c r="N1" s="235"/>
+      <c r="O1" s="235"/>
+      <c r="P1" s="235"/>
+      <c r="Q1" s="235"/>
+      <c r="R1" s="235"/>
+      <c r="S1" s="235"/>
+      <c r="T1" s="235"/>
+      <c r="U1" s="235"/>
+      <c r="V1" s="235"/>
+      <c r="W1" s="235"/>
+      <c r="X1" s="235"/>
+      <c r="Y1" s="235"/>
+      <c r="Z1" s="235"/>
+      <c r="AA1" s="235"/>
+      <c r="AB1" s="235"/>
+      <c r="AC1" s="235"/>
+      <c r="AD1" s="235"/>
+      <c r="AE1" s="235"/>
+      <c r="AF1" s="235"/>
+      <c r="AG1" s="235"/>
+      <c r="AH1" s="235"/>
+      <c r="AI1" s="235"/>
+      <c r="AJ1" s="235"/>
+      <c r="AK1" s="235"/>
+      <c r="AL1" s="235"/>
+      <c r="AM1" s="235"/>
+      <c r="AN1" s="235"/>
+      <c r="AO1" s="235"/>
       <c r="AP1" s="41"/>
       <c r="AQ1" s="41"/>
       <c r="AR1" s="41"/>
@@ -5483,97 +5481,97 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" s="43"/>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="237" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="43"/>
-      <c r="D3" s="207" t="s">
+      <c r="D3" s="237" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="43"/>
-      <c r="F3" s="192" t="s">
+      <c r="F3" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192"/>
-      <c r="L3" s="192" t="s">
+      <c r="G3" s="238"/>
+      <c r="H3" s="238"/>
+      <c r="L3" s="238" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="192"/>
-      <c r="N3" s="192"/>
-      <c r="P3" s="192" t="s">
+      <c r="M3" s="238"/>
+      <c r="N3" s="238"/>
+      <c r="P3" s="238" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="192"/>
-      <c r="R3" s="192"/>
-      <c r="S3" s="192"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="238"/>
       <c r="T3" s="148"/>
-      <c r="U3" s="192" t="s">
+      <c r="U3" s="238" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="192"/>
+      <c r="V3" s="238"/>
       <c r="W3" s="45"/>
-      <c r="X3" s="192" t="s">
+      <c r="X3" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="Y3" s="192"/>
+      <c r="Y3" s="238"/>
       <c r="Z3" s="148"/>
-      <c r="AA3" s="192" t="s">
+      <c r="AA3" s="238" t="s">
         <v>8</v>
       </c>
-      <c r="AB3" s="192"/>
+      <c r="AB3" s="238"/>
     </row>
     <row r="4" spans="1:48" ht="14.45" customHeight="1">
       <c r="A4" s="43"/>
-      <c r="B4" s="207"/>
+      <c r="B4" s="237"/>
       <c r="C4" s="43"/>
-      <c r="D4" s="207"/>
+      <c r="D4" s="237"/>
       <c r="E4" s="43"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="L4" s="192"/>
-      <c r="M4" s="192"/>
-      <c r="N4" s="192"/>
-      <c r="P4" s="192"/>
-      <c r="Q4" s="192"/>
-      <c r="R4" s="192"/>
-      <c r="S4" s="192"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
+      <c r="H4" s="238"/>
+      <c r="L4" s="238"/>
+      <c r="M4" s="238"/>
+      <c r="N4" s="238"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="238"/>
       <c r="T4" s="148"/>
-      <c r="U4" s="192"/>
-      <c r="V4" s="192"/>
+      <c r="U4" s="238"/>
+      <c r="V4" s="238"/>
       <c r="W4" s="45"/>
-      <c r="X4" s="192"/>
-      <c r="Y4" s="192"/>
+      <c r="X4" s="238"/>
+      <c r="Y4" s="238"/>
       <c r="Z4" s="148"/>
-      <c r="AA4" s="192"/>
-      <c r="AB4" s="192"/>
+      <c r="AA4" s="238"/>
+      <c r="AB4" s="238"/>
     </row>
     <row r="5" spans="1:48" ht="18.75" customHeight="1">
       <c r="A5" s="43"/>
-      <c r="B5" s="208" t="s">
+      <c r="B5" s="229" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="43"/>
-      <c r="D5" s="208" t="s">
+      <c r="D5" s="229" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="43"/>
-      <c r="F5" s="211" t="s">
+      <c r="F5" s="233" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="L5" s="206" t="s">
+      <c r="G5" s="233"/>
+      <c r="H5" s="233"/>
+      <c r="L5" s="236" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="206"/>
-      <c r="N5" s="206"/>
+      <c r="M5" s="236"/>
+      <c r="N5" s="236"/>
       <c r="R5" s="148"/>
       <c r="S5" s="148"/>
       <c r="T5" s="148"/>
       <c r="U5" s="148"/>
-      <c r="V5" s="195"/>
+      <c r="V5" s="245"/>
       <c r="W5" s="148"/>
       <c r="X5" s="148"/>
       <c r="Y5" s="148"/>
@@ -5583,68 +5581,68 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" s="43"/>
-      <c r="B6" s="208"/>
+      <c r="B6" s="229"/>
       <c r="C6" s="43"/>
-      <c r="D6" s="208"/>
+      <c r="D6" s="229"/>
       <c r="E6" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="211"/>
-      <c r="G6" s="211"/>
-      <c r="H6" s="211"/>
-      <c r="I6" s="205" t="s">
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
+      <c r="H6" s="233"/>
+      <c r="I6" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
-      <c r="L6" s="206"/>
-      <c r="M6" s="206"/>
-      <c r="N6" s="206"/>
+      <c r="J6" s="231"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="236"/>
+      <c r="N6" s="236"/>
       <c r="R6" s="148"/>
       <c r="S6" s="148"/>
       <c r="T6" s="148"/>
       <c r="U6" s="148"/>
-      <c r="V6" s="195"/>
+      <c r="V6" s="245"/>
     </row>
     <row r="7" spans="1:48">
       <c r="A7" s="43"/>
-      <c r="B7" s="208"/>
+      <c r="B7" s="229"/>
       <c r="C7" s="43"/>
-      <c r="D7" s="208"/>
+      <c r="D7" s="229"/>
       <c r="E7" s="43"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="L7" s="206"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="206"/>
+      <c r="F7" s="233"/>
+      <c r="G7" s="233"/>
+      <c r="H7" s="233"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
       <c r="R7" s="148"/>
       <c r="S7" s="148"/>
       <c r="T7" s="148"/>
     </row>
     <row r="8" spans="1:48" ht="14.45" customHeight="1">
-      <c r="B8" s="208"/>
+      <c r="B8" s="229"/>
       <c r="C8" s="45"/>
-      <c r="D8" s="208"/>
-      <c r="L8" s="206"/>
-      <c r="M8" s="206"/>
-      <c r="N8" s="206"/>
+      <c r="D8" s="229"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
       <c r="R8" s="148"/>
       <c r="S8" s="148"/>
       <c r="T8" s="148"/>
     </row>
     <row r="9" spans="1:48" ht="14.45" customHeight="1">
-      <c r="B9" s="208"/>
+      <c r="B9" s="229"/>
       <c r="C9" s="45"/>
-      <c r="D9" s="208"/>
-      <c r="F9" s="211" t="s">
+      <c r="D9" s="229"/>
+      <c r="F9" s="233" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="211"/>
-      <c r="H9" s="211"/>
-      <c r="L9" s="206"/>
-      <c r="M9" s="206"/>
-      <c r="N9" s="206"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
       <c r="R9" s="148"/>
       <c r="S9" s="148"/>
       <c r="T9" s="148"/>
@@ -5659,28 +5657,28 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" s="46"/>
-      <c r="B10" s="208"/>
+      <c r="B10" s="229"/>
       <c r="C10" s="45"/>
-      <c r="D10" s="208"/>
+      <c r="D10" s="229"/>
       <c r="E10" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="211"/>
-      <c r="G10" s="211"/>
-      <c r="H10" s="211"/>
-      <c r="I10" s="205" t="s">
+      <c r="F10" s="233"/>
+      <c r="G10" s="233"/>
+      <c r="H10" s="233"/>
+      <c r="I10" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205"/>
-      <c r="L10" s="206"/>
-      <c r="M10" s="206"/>
-      <c r="N10" s="206"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
       <c r="R10" s="148"/>
       <c r="S10" s="148"/>
       <c r="T10" s="148"/>
       <c r="U10" s="148"/>
-      <c r="V10" s="196"/>
+      <c r="V10" s="241"/>
       <c r="W10" s="148"/>
       <c r="X10" s="148"/>
       <c r="Y10" s="148"/>
@@ -5690,20 +5688,20 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" s="42"/>
-      <c r="B11" s="208"/>
+      <c r="B11" s="229"/>
       <c r="C11" s="45"/>
-      <c r="D11" s="208"/>
-      <c r="F11" s="211"/>
-      <c r="G11" s="211"/>
-      <c r="H11" s="211"/>
-      <c r="L11" s="206"/>
-      <c r="M11" s="206"/>
-      <c r="N11" s="206"/>
+      <c r="D11" s="229"/>
+      <c r="F11" s="233"/>
+      <c r="G11" s="233"/>
+      <c r="H11" s="233"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
       <c r="R11" s="148"/>
       <c r="S11" s="148"/>
       <c r="T11" s="148"/>
       <c r="U11" s="148"/>
-      <c r="V11" s="196"/>
+      <c r="V11" s="241"/>
       <c r="W11" s="148"/>
       <c r="X11" s="148"/>
       <c r="Y11" s="148"/>
@@ -5713,8 +5711,8 @@
     </row>
     <row r="12" spans="1:48" ht="14.45" customHeight="1">
       <c r="A12" s="47"/>
-      <c r="B12" s="208"/>
-      <c r="D12" s="208"/>
+      <c r="B12" s="229"/>
+      <c r="D12" s="229"/>
       <c r="R12" s="148"/>
       <c r="S12" s="148"/>
       <c r="T12" s="148"/>
@@ -5729,105 +5727,105 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" s="42"/>
-      <c r="B13" s="208"/>
+      <c r="B13" s="229"/>
       <c r="C13" s="45"/>
-      <c r="D13" s="208"/>
-      <c r="F13" s="200" t="s">
+      <c r="D13" s="229"/>
+      <c r="F13" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="200"/>
-      <c r="H13" s="200"/>
-      <c r="L13" s="213" t="s">
+      <c r="G13" s="232"/>
+      <c r="H13" s="232"/>
+      <c r="L13" s="230" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="213"/>
-      <c r="N13" s="213"/>
-      <c r="O13" s="194" t="s">
+      <c r="M13" s="230"/>
+      <c r="N13" s="230"/>
+      <c r="O13" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="193" t="s">
+      <c r="P13" s="234" t="s">
         <v>18</v>
       </c>
-      <c r="Q13" s="193"/>
-      <c r="R13" s="193"/>
-      <c r="S13" s="193"/>
-      <c r="T13" s="194" t="s">
+      <c r="Q13" s="234"/>
+      <c r="R13" s="234"/>
+      <c r="S13" s="234"/>
+      <c r="T13" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="U13" s="201" t="s">
+      <c r="U13" s="247" t="s">
         <v>19</v>
       </c>
-      <c r="V13" s="202"/>
-      <c r="W13" s="194" t="s">
+      <c r="V13" s="248"/>
+      <c r="W13" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="X13" s="193" t="s">
+      <c r="X13" s="234" t="s">
         <v>20</v>
       </c>
-      <c r="Y13" s="193"/>
-      <c r="Z13" s="194" t="s">
+      <c r="Y13" s="234"/>
+      <c r="Z13" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="AA13" s="197" t="s">
+      <c r="AA13" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="AB13" s="197"/>
+      <c r="AB13" s="246"/>
     </row>
     <row r="14" spans="1:48" ht="16.5" customHeight="1">
       <c r="A14" s="48"/>
-      <c r="B14" s="208"/>
+      <c r="B14" s="229"/>
       <c r="C14" s="45"/>
-      <c r="D14" s="208"/>
-      <c r="F14" s="200"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="200"/>
-      <c r="I14" s="205" t="s">
+      <c r="D14" s="229"/>
+      <c r="F14" s="232"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="232"/>
+      <c r="I14" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J14" s="205"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="213"/>
-      <c r="M14" s="213"/>
-      <c r="N14" s="213"/>
-      <c r="O14" s="194"/>
-      <c r="P14" s="193"/>
-      <c r="Q14" s="193"/>
-      <c r="R14" s="193"/>
-      <c r="S14" s="193"/>
-      <c r="T14" s="194"/>
-      <c r="U14" s="202"/>
-      <c r="V14" s="202"/>
-      <c r="W14" s="194"/>
-      <c r="X14" s="193"/>
-      <c r="Y14" s="193"/>
-      <c r="Z14" s="194"/>
-      <c r="AA14" s="197"/>
-      <c r="AB14" s="197"/>
+      <c r="J14" s="231"/>
+      <c r="K14" s="231"/>
+      <c r="L14" s="230"/>
+      <c r="M14" s="230"/>
+      <c r="N14" s="230"/>
+      <c r="O14" s="244"/>
+      <c r="P14" s="234"/>
+      <c r="Q14" s="234"/>
+      <c r="R14" s="234"/>
+      <c r="S14" s="234"/>
+      <c r="T14" s="244"/>
+      <c r="U14" s="248"/>
+      <c r="V14" s="248"/>
+      <c r="W14" s="244"/>
+      <c r="X14" s="234"/>
+      <c r="Y14" s="234"/>
+      <c r="Z14" s="244"/>
+      <c r="AA14" s="246"/>
+      <c r="AB14" s="246"/>
     </row>
     <row r="15" spans="1:48">
       <c r="A15" s="48"/>
-      <c r="B15" s="208"/>
+      <c r="B15" s="229"/>
       <c r="C15" s="45"/>
-      <c r="D15" s="208"/>
+      <c r="D15" s="229"/>
       <c r="E15" s="48"/>
-      <c r="F15" s="200"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="200"/>
-      <c r="L15" s="213"/>
-      <c r="M15" s="213"/>
-      <c r="N15" s="213"/>
+      <c r="F15" s="232"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="232"/>
+      <c r="L15" s="230"/>
+      <c r="M15" s="230"/>
+      <c r="N15" s="230"/>
       <c r="Z15" s="148"/>
       <c r="AA15" s="148"/>
       <c r="AB15" s="148"/>
     </row>
     <row r="16" spans="1:48">
       <c r="A16" s="48"/>
-      <c r="B16" s="208"/>
+      <c r="B16" s="229"/>
       <c r="C16" s="48"/>
-      <c r="D16" s="208"/>
-      <c r="F16" s="200"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="200"/>
+      <c r="D16" s="229"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="232"/>
       <c r="O16" s="149"/>
       <c r="R16" s="148"/>
       <c r="S16" s="148"/>
@@ -5840,67 +5838,67 @@
       <c r="Z16" s="148"/>
       <c r="AA16" s="148"/>
       <c r="AB16" s="148"/>
-      <c r="AI16" s="209"/>
+      <c r="AI16" s="239"/>
     </row>
     <row r="17" spans="1:35" ht="15" customHeight="1">
       <c r="A17" s="48"/>
-      <c r="B17" s="208"/>
+      <c r="B17" s="229"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="208"/>
+      <c r="D17" s="229"/>
       <c r="E17" s="48"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="205" t="s">
+      <c r="F17" s="232"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="232"/>
+      <c r="I17" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="205"/>
-      <c r="K17" s="205"/>
-      <c r="L17" s="200" t="s">
+      <c r="J17" s="231"/>
+      <c r="K17" s="231"/>
+      <c r="L17" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="200"/>
-      <c r="N17" s="200"/>
-      <c r="O17" s="194" t="s">
+      <c r="M17" s="232"/>
+      <c r="N17" s="232"/>
+      <c r="O17" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="P17" s="193" t="s">
+      <c r="P17" s="234" t="s">
         <v>23</v>
       </c>
-      <c r="Q17" s="193"/>
-      <c r="R17" s="193"/>
-      <c r="S17" s="193"/>
+      <c r="Q17" s="234"/>
+      <c r="R17" s="234"/>
+      <c r="S17" s="234"/>
       <c r="T17" s="148"/>
       <c r="U17" s="148"/>
-      <c r="V17" s="196"/>
+      <c r="V17" s="241"/>
       <c r="W17" s="148"/>
       <c r="X17" s="148"/>
       <c r="Y17" s="148"/>
       <c r="Z17" s="148"/>
       <c r="AA17" s="148"/>
       <c r="AB17" s="148"/>
-      <c r="AI17" s="209"/>
+      <c r="AI17" s="239"/>
     </row>
     <row r="18" spans="1:35">
       <c r="A18" s="48"/>
-      <c r="B18" s="208"/>
+      <c r="B18" s="229"/>
       <c r="C18" s="48"/>
-      <c r="D18" s="208"/>
+      <c r="D18" s="229"/>
       <c r="E18" s="48"/>
-      <c r="F18" s="200"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="200"/>
-      <c r="L18" s="200"/>
-      <c r="M18" s="200"/>
-      <c r="N18" s="200"/>
-      <c r="O18" s="194"/>
-      <c r="P18" s="193"/>
-      <c r="Q18" s="193"/>
-      <c r="R18" s="193"/>
-      <c r="S18" s="193"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="232"/>
+      <c r="L18" s="232"/>
+      <c r="M18" s="232"/>
+      <c r="N18" s="232"/>
+      <c r="O18" s="244"/>
+      <c r="P18" s="234"/>
+      <c r="Q18" s="234"/>
+      <c r="R18" s="234"/>
+      <c r="S18" s="234"/>
       <c r="T18" s="148"/>
       <c r="U18" s="148"/>
-      <c r="V18" s="196"/>
+      <c r="V18" s="241"/>
       <c r="W18" s="148"/>
       <c r="X18" s="148"/>
       <c r="Y18" s="148"/>
@@ -5910,15 +5908,15 @@
     </row>
     <row r="19" spans="1:35">
       <c r="A19" s="48"/>
-      <c r="B19" s="208"/>
+      <c r="B19" s="229"/>
       <c r="C19" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="208"/>
+      <c r="D19" s="229"/>
       <c r="E19" s="48"/>
-      <c r="F19" s="200"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="200"/>
+      <c r="F19" s="232"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="232"/>
       <c r="R19" s="148"/>
       <c r="S19" s="148"/>
       <c r="T19" s="148"/>
@@ -5933,198 +5931,198 @@
     </row>
     <row r="20" spans="1:35" ht="15" customHeight="1">
       <c r="A20" s="48"/>
-      <c r="B20" s="208"/>
+      <c r="B20" s="229"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="208"/>
+      <c r="D20" s="229"/>
       <c r="E20" s="50"/>
-      <c r="F20" s="200"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="200"/>
-      <c r="L20" s="200" t="s">
+      <c r="F20" s="232"/>
+      <c r="G20" s="232"/>
+      <c r="H20" s="232"/>
+      <c r="L20" s="232" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="200"/>
-      <c r="N20" s="200"/>
-      <c r="O20" s="294" t="s">
+      <c r="M20" s="232"/>
+      <c r="N20" s="232"/>
+      <c r="O20" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="P20" s="285" t="s">
+      <c r="P20" s="204" t="s">
         <v>25</v>
       </c>
-      <c r="Q20" s="286"/>
-      <c r="R20" s="286"/>
-      <c r="S20" s="287"/>
-      <c r="T20" s="294" t="s">
+      <c r="Q20" s="225"/>
+      <c r="R20" s="225"/>
+      <c r="S20" s="205"/>
+      <c r="T20" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="U20" s="285" t="s">
+      <c r="U20" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="V20" s="287"/>
-      <c r="W20" s="294" t="s">
+      <c r="V20" s="205"/>
+      <c r="W20" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="X20" s="273" t="s">
+      <c r="X20" s="192" t="s">
         <v>27</v>
       </c>
-      <c r="Y20" s="274"/>
+      <c r="Y20" s="193"/>
       <c r="AB20" s="148"/>
     </row>
     <row r="21" spans="1:35">
       <c r="A21" s="48"/>
-      <c r="B21" s="208"/>
+      <c r="B21" s="229"/>
       <c r="C21" s="48"/>
-      <c r="D21" s="208"/>
+      <c r="D21" s="229"/>
       <c r="E21" s="50"/>
-      <c r="F21" s="200"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="200"/>
-      <c r="L21" s="200"/>
-      <c r="M21" s="200"/>
-      <c r="N21" s="200"/>
-      <c r="O21" s="295"/>
-      <c r="P21" s="288"/>
-      <c r="Q21" s="289"/>
-      <c r="R21" s="289"/>
-      <c r="S21" s="290"/>
-      <c r="T21" s="295"/>
-      <c r="U21" s="288"/>
-      <c r="V21" s="290"/>
-      <c r="W21" s="295"/>
-      <c r="X21" s="275"/>
-      <c r="Y21" s="276"/>
+      <c r="F21" s="232"/>
+      <c r="G21" s="232"/>
+      <c r="H21" s="232"/>
+      <c r="L21" s="232"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="232"/>
+      <c r="O21" s="211"/>
+      <c r="P21" s="206"/>
+      <c r="Q21" s="226"/>
+      <c r="R21" s="226"/>
+      <c r="S21" s="207"/>
+      <c r="T21" s="211"/>
+      <c r="U21" s="206"/>
+      <c r="V21" s="207"/>
+      <c r="W21" s="211"/>
+      <c r="X21" s="194"/>
+      <c r="Y21" s="195"/>
     </row>
     <row r="22" spans="1:35">
       <c r="A22" s="50"/>
-      <c r="B22" s="208"/>
+      <c r="B22" s="229"/>
       <c r="C22" s="50"/>
-      <c r="D22" s="208"/>
+      <c r="D22" s="229"/>
       <c r="E22" s="50"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="200"/>
-      <c r="L22" s="200"/>
-      <c r="M22" s="200"/>
-      <c r="N22" s="200"/>
-      <c r="O22" s="295"/>
-      <c r="P22" s="288"/>
-      <c r="Q22" s="289"/>
-      <c r="R22" s="289"/>
-      <c r="S22" s="290"/>
-      <c r="T22" s="296"/>
-      <c r="U22" s="288"/>
-      <c r="V22" s="290"/>
-      <c r="W22" s="296"/>
-      <c r="X22" s="277"/>
-      <c r="Y22" s="278"/>
+      <c r="F22" s="232"/>
+      <c r="G22" s="232"/>
+      <c r="H22" s="232"/>
+      <c r="L22" s="232"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="232"/>
+      <c r="O22" s="211"/>
+      <c r="P22" s="206"/>
+      <c r="Q22" s="226"/>
+      <c r="R22" s="226"/>
+      <c r="S22" s="207"/>
+      <c r="T22" s="212"/>
+      <c r="U22" s="206"/>
+      <c r="V22" s="207"/>
+      <c r="W22" s="212"/>
+      <c r="X22" s="196"/>
+      <c r="Y22" s="197"/>
     </row>
     <row r="23" spans="1:35" ht="15" customHeight="1">
       <c r="A23" s="50"/>
-      <c r="B23" s="208"/>
+      <c r="B23" s="229"/>
       <c r="C23" s="50"/>
-      <c r="D23" s="208"/>
+      <c r="D23" s="229"/>
       <c r="E23" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="200"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="200"/>
-      <c r="I23" s="205" t="s">
+      <c r="F23" s="232"/>
+      <c r="G23" s="232"/>
+      <c r="H23" s="232"/>
+      <c r="I23" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="205"/>
-      <c r="K23" s="205"/>
-      <c r="L23" s="200"/>
-      <c r="M23" s="200"/>
-      <c r="N23" s="200"/>
-      <c r="O23" s="295"/>
-      <c r="P23" s="288"/>
-      <c r="Q23" s="289"/>
-      <c r="R23" s="289"/>
-      <c r="S23" s="290"/>
-      <c r="U23" s="288"/>
-      <c r="V23" s="290"/>
+      <c r="J23" s="231"/>
+      <c r="K23" s="231"/>
+      <c r="L23" s="232"/>
+      <c r="M23" s="232"/>
+      <c r="N23" s="232"/>
+      <c r="O23" s="211"/>
+      <c r="P23" s="206"/>
+      <c r="Q23" s="226"/>
+      <c r="R23" s="226"/>
+      <c r="S23" s="207"/>
+      <c r="U23" s="206"/>
+      <c r="V23" s="207"/>
       <c r="X23" s="152"/>
       <c r="Y23" s="152"/>
     </row>
     <row r="24" spans="1:35" ht="18.75" customHeight="1">
       <c r="A24" s="50"/>
-      <c r="B24" s="208"/>
+      <c r="B24" s="229"/>
       <c r="C24" s="50"/>
-      <c r="D24" s="208"/>
+      <c r="D24" s="229"/>
       <c r="E24" s="50"/>
-      <c r="F24" s="200"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="200"/>
-      <c r="L24" s="200"/>
-      <c r="M24" s="200"/>
-      <c r="N24" s="200"/>
-      <c r="O24" s="295"/>
-      <c r="P24" s="288"/>
-      <c r="Q24" s="289"/>
-      <c r="R24" s="289"/>
-      <c r="S24" s="290"/>
-      <c r="T24" s="294" t="s">
+      <c r="F24" s="232"/>
+      <c r="G24" s="232"/>
+      <c r="H24" s="232"/>
+      <c r="L24" s="232"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="232"/>
+      <c r="O24" s="211"/>
+      <c r="P24" s="206"/>
+      <c r="Q24" s="226"/>
+      <c r="R24" s="226"/>
+      <c r="S24" s="207"/>
+      <c r="T24" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="U24" s="288"/>
-      <c r="V24" s="290"/>
-      <c r="W24" s="294" t="s">
+      <c r="U24" s="206"/>
+      <c r="V24" s="207"/>
+      <c r="W24" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="X24" s="279" t="s">
+      <c r="X24" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="Y24" s="280"/>
+      <c r="Y24" s="199"/>
     </row>
     <row r="25" spans="1:35">
-      <c r="B25" s="208"/>
-      <c r="D25" s="208"/>
-      <c r="F25" s="200"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="200"/>
-      <c r="L25" s="200"/>
-      <c r="M25" s="200"/>
-      <c r="N25" s="200"/>
-      <c r="O25" s="295"/>
-      <c r="P25" s="288"/>
-      <c r="Q25" s="289"/>
-      <c r="R25" s="289"/>
-      <c r="S25" s="290"/>
-      <c r="T25" s="295"/>
-      <c r="U25" s="288"/>
-      <c r="V25" s="290"/>
-      <c r="W25" s="295"/>
-      <c r="X25" s="281"/>
-      <c r="Y25" s="282"/>
+      <c r="B25" s="229"/>
+      <c r="D25" s="229"/>
+      <c r="F25" s="232"/>
+      <c r="G25" s="232"/>
+      <c r="H25" s="232"/>
+      <c r="L25" s="232"/>
+      <c r="M25" s="232"/>
+      <c r="N25" s="232"/>
+      <c r="O25" s="211"/>
+      <c r="P25" s="206"/>
+      <c r="Q25" s="226"/>
+      <c r="R25" s="226"/>
+      <c r="S25" s="207"/>
+      <c r="T25" s="211"/>
+      <c r="U25" s="206"/>
+      <c r="V25" s="207"/>
+      <c r="W25" s="211"/>
+      <c r="X25" s="200"/>
+      <c r="Y25" s="201"/>
     </row>
     <row r="26" spans="1:35" ht="15" customHeight="1">
-      <c r="B26" s="208"/>
-      <c r="D26" s="208"/>
-      <c r="F26" s="200"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="200"/>
-      <c r="L26" s="200"/>
-      <c r="M26" s="200"/>
-      <c r="N26" s="200"/>
-      <c r="O26" s="296"/>
-      <c r="P26" s="291"/>
-      <c r="Q26" s="292"/>
-      <c r="R26" s="292"/>
-      <c r="S26" s="293"/>
-      <c r="T26" s="296"/>
-      <c r="U26" s="291"/>
-      <c r="V26" s="293"/>
-      <c r="W26" s="296"/>
-      <c r="X26" s="283"/>
-      <c r="Y26" s="284"/>
+      <c r="B26" s="229"/>
+      <c r="D26" s="229"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="232"/>
+      <c r="H26" s="232"/>
+      <c r="L26" s="232"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="232"/>
+      <c r="O26" s="212"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="227"/>
+      <c r="R26" s="227"/>
+      <c r="S26" s="209"/>
+      <c r="T26" s="212"/>
+      <c r="U26" s="208"/>
+      <c r="V26" s="209"/>
+      <c r="W26" s="212"/>
+      <c r="X26" s="202"/>
+      <c r="Y26" s="203"/>
     </row>
     <row r="27" spans="1:35">
-      <c r="B27" s="208"/>
-      <c r="D27" s="208"/>
-      <c r="F27" s="200"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="200"/>
+      <c r="B27" s="229"/>
+      <c r="D27" s="229"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="232"/>
       <c r="R27" s="148"/>
       <c r="S27" s="148"/>
       <c r="T27" s="148"/>
@@ -6134,21 +6132,21 @@
       <c r="X27" s="148"/>
     </row>
     <row r="28" spans="1:35">
-      <c r="B28" s="208"/>
-      <c r="D28" s="208"/>
-      <c r="F28" s="200"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="200"/>
-      <c r="I28" s="205" t="s">
+      <c r="B28" s="229"/>
+      <c r="D28" s="229"/>
+      <c r="F28" s="232"/>
+      <c r="G28" s="232"/>
+      <c r="H28" s="232"/>
+      <c r="I28" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J28" s="205"/>
-      <c r="K28" s="205"/>
-      <c r="L28" s="212" t="s">
+      <c r="J28" s="231"/>
+      <c r="K28" s="231"/>
+      <c r="L28" s="228" t="s">
         <v>29</v>
       </c>
-      <c r="M28" s="212"/>
-      <c r="N28" s="212"/>
+      <c r="M28" s="228"/>
+      <c r="N28" s="228"/>
       <c r="R28" s="148"/>
       <c r="S28" s="148"/>
       <c r="T28" s="148"/>
@@ -6162,14 +6160,14 @@
       <c r="AB28" s="148"/>
     </row>
     <row r="29" spans="1:35" ht="15" customHeight="1">
-      <c r="B29" s="208"/>
-      <c r="D29" s="208"/>
-      <c r="F29" s="200"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="200"/>
-      <c r="L29" s="212"/>
-      <c r="M29" s="212"/>
-      <c r="N29" s="212"/>
+      <c r="B29" s="229"/>
+      <c r="D29" s="229"/>
+      <c r="F29" s="232"/>
+      <c r="G29" s="232"/>
+      <c r="H29" s="232"/>
+      <c r="L29" s="228"/>
+      <c r="M29" s="228"/>
+      <c r="N29" s="228"/>
       <c r="R29" s="148"/>
       <c r="S29" s="148"/>
       <c r="T29" s="148"/>
@@ -6183,11 +6181,11 @@
       <c r="AB29" s="148"/>
     </row>
     <row r="30" spans="1:35">
-      <c r="B30" s="208"/>
-      <c r="D30" s="208"/>
-      <c r="F30" s="200"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="200"/>
+      <c r="B30" s="229"/>
+      <c r="D30" s="229"/>
+      <c r="F30" s="232"/>
+      <c r="G30" s="232"/>
+      <c r="H30" s="232"/>
       <c r="R30" s="148"/>
       <c r="S30" s="148"/>
       <c r="T30" s="148"/>
@@ -6201,21 +6199,21 @@
       <c r="AB30" s="148"/>
     </row>
     <row r="31" spans="1:35">
-      <c r="B31" s="208"/>
-      <c r="D31" s="208"/>
-      <c r="F31" s="200"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="200"/>
-      <c r="I31" s="205" t="s">
+      <c r="B31" s="229"/>
+      <c r="D31" s="229"/>
+      <c r="F31" s="232"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J31" s="205"/>
-      <c r="K31" s="205"/>
-      <c r="L31" s="212" t="s">
+      <c r="J31" s="231"/>
+      <c r="K31" s="231"/>
+      <c r="L31" s="228" t="s">
         <v>30</v>
       </c>
-      <c r="M31" s="212"/>
-      <c r="N31" s="212"/>
+      <c r="M31" s="228"/>
+      <c r="N31" s="228"/>
       <c r="R31" s="148"/>
       <c r="S31" s="148"/>
       <c r="T31" s="148"/>
@@ -6229,285 +6227,285 @@
       <c r="AB31" s="148"/>
     </row>
     <row r="32" spans="1:35" ht="15" customHeight="1">
-      <c r="B32" s="208"/>
-      <c r="D32" s="208"/>
-      <c r="F32" s="200"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="200"/>
-      <c r="L32" s="212"/>
-      <c r="M32" s="212"/>
-      <c r="N32" s="212"/>
+      <c r="B32" s="229"/>
+      <c r="D32" s="229"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="232"/>
+      <c r="L32" s="228"/>
+      <c r="M32" s="228"/>
+      <c r="N32" s="228"/>
       <c r="Z32" s="148"/>
       <c r="AA32" s="148"/>
       <c r="AB32" s="148"/>
     </row>
     <row r="33" spans="2:35">
-      <c r="B33" s="208"/>
-      <c r="D33" s="208"/>
-      <c r="F33" s="200"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="200"/>
+      <c r="B33" s="229"/>
+      <c r="D33" s="229"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
       <c r="Z33" s="148"/>
       <c r="AA33" s="148"/>
       <c r="AB33" s="148"/>
     </row>
     <row r="34" spans="2:35">
-      <c r="B34" s="208"/>
-      <c r="D34" s="208"/>
-      <c r="F34" s="200"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="200"/>
-      <c r="I34" s="205" t="s">
+      <c r="B34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="F34" s="232"/>
+      <c r="G34" s="232"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J34" s="205"/>
-      <c r="K34" s="205"/>
-      <c r="L34" s="212" t="s">
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="228" t="s">
         <v>31</v>
       </c>
-      <c r="M34" s="212"/>
-      <c r="N34" s="212"/>
-      <c r="AH34" s="210"/>
-      <c r="AI34" s="210"/>
+      <c r="M34" s="228"/>
+      <c r="N34" s="228"/>
+      <c r="AH34" s="240"/>
+      <c r="AI34" s="240"/>
     </row>
     <row r="35" spans="2:35">
-      <c r="B35" s="208"/>
-      <c r="D35" s="208"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="200"/>
-      <c r="L35" s="212"/>
-      <c r="M35" s="212"/>
-      <c r="N35" s="212"/>
+      <c r="B35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
+      <c r="H35" s="232"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
+      <c r="N35" s="228"/>
     </row>
     <row r="36" spans="2:35">
-      <c r="B36" s="208"/>
-      <c r="D36" s="208"/>
-      <c r="F36" s="200"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="200"/>
+      <c r="B36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="F36" s="232"/>
+      <c r="G36" s="232"/>
+      <c r="H36" s="232"/>
     </row>
     <row r="37" spans="2:35" ht="18.75" customHeight="1">
-      <c r="B37" s="208"/>
-      <c r="D37" s="208"/>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="200"/>
-      <c r="L37" s="199" t="s">
+      <c r="B37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="F37" s="232"/>
+      <c r="G37" s="232"/>
+      <c r="H37" s="232"/>
+      <c r="L37" s="243" t="s">
         <v>25</v>
       </c>
-      <c r="M37" s="199"/>
-      <c r="N37" s="199"/>
-      <c r="P37" s="199" t="s">
+      <c r="M37" s="243"/>
+      <c r="N37" s="243"/>
+      <c r="P37" s="243" t="s">
         <v>26</v>
       </c>
-      <c r="Q37" s="199"/>
-      <c r="R37" s="199"/>
-      <c r="S37" s="199"/>
-      <c r="T37" s="203" t="s">
+      <c r="Q37" s="243"/>
+      <c r="R37" s="243"/>
+      <c r="S37" s="243"/>
+      <c r="T37" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="U37" s="273" t="s">
+      <c r="U37" s="192" t="s">
         <v>27</v>
       </c>
-      <c r="V37" s="274"/>
-      <c r="W37" s="298"/>
-      <c r="X37" s="299"/>
+      <c r="V37" s="193"/>
+      <c r="W37" s="213"/>
+      <c r="X37" s="214"/>
       <c r="Y37" s="151"/>
       <c r="Z37" s="151"/>
     </row>
     <row r="38" spans="2:35">
-      <c r="B38" s="208"/>
-      <c r="D38" s="208"/>
-      <c r="F38" s="200"/>
-      <c r="G38" s="200"/>
-      <c r="H38" s="200"/>
-      <c r="L38" s="199"/>
-      <c r="M38" s="199"/>
-      <c r="N38" s="199"/>
-      <c r="P38" s="199"/>
-      <c r="Q38" s="199"/>
-      <c r="R38" s="199"/>
-      <c r="S38" s="199"/>
-      <c r="T38" s="203"/>
-      <c r="U38" s="275"/>
-      <c r="V38" s="276"/>
-      <c r="W38" s="300"/>
-      <c r="X38" s="301"/>
+      <c r="B38" s="229"/>
+      <c r="D38" s="229"/>
+      <c r="F38" s="232"/>
+      <c r="G38" s="232"/>
+      <c r="H38" s="232"/>
+      <c r="L38" s="243"/>
+      <c r="M38" s="243"/>
+      <c r="N38" s="243"/>
+      <c r="P38" s="243"/>
+      <c r="Q38" s="243"/>
+      <c r="R38" s="243"/>
+      <c r="S38" s="243"/>
+      <c r="T38" s="249"/>
+      <c r="U38" s="194"/>
+      <c r="V38" s="195"/>
+      <c r="W38" s="215"/>
+      <c r="X38" s="216"/>
       <c r="Y38" s="151"/>
       <c r="Z38" s="151"/>
     </row>
     <row r="39" spans="2:35">
-      <c r="B39" s="208"/>
-      <c r="D39" s="208"/>
-      <c r="F39" s="200"/>
-      <c r="G39" s="200"/>
-      <c r="H39" s="200"/>
-      <c r="L39" s="199"/>
-      <c r="M39" s="199"/>
-      <c r="N39" s="199"/>
+      <c r="B39" s="229"/>
+      <c r="D39" s="229"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
+      <c r="L39" s="243"/>
+      <c r="M39" s="243"/>
+      <c r="N39" s="243"/>
       <c r="O39" s="150" t="s">
         <v>13</v>
       </c>
-      <c r="P39" s="199"/>
-      <c r="Q39" s="199"/>
-      <c r="R39" s="199"/>
-      <c r="S39" s="199"/>
-      <c r="T39" s="203"/>
-      <c r="U39" s="277"/>
-      <c r="V39" s="278"/>
-      <c r="W39" s="302"/>
-      <c r="X39" s="303"/>
+      <c r="P39" s="243"/>
+      <c r="Q39" s="243"/>
+      <c r="R39" s="243"/>
+      <c r="S39" s="243"/>
+      <c r="T39" s="249"/>
+      <c r="U39" s="196"/>
+      <c r="V39" s="197"/>
+      <c r="W39" s="217"/>
+      <c r="X39" s="218"/>
       <c r="Y39" s="151"/>
       <c r="Z39" s="151"/>
     </row>
     <row r="40" spans="2:35">
-      <c r="B40" s="208"/>
-      <c r="D40" s="208"/>
-      <c r="F40" s="200"/>
-      <c r="G40" s="200"/>
-      <c r="H40" s="200"/>
-      <c r="I40" s="205" t="s">
+      <c r="B40" s="229"/>
+      <c r="D40" s="229"/>
+      <c r="F40" s="232"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="J40" s="205"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="199"/>
-      <c r="M40" s="199"/>
-      <c r="N40" s="199"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="243"/>
+      <c r="M40" s="243"/>
+      <c r="N40" s="243"/>
       <c r="O40" s="153"/>
-      <c r="P40" s="199"/>
-      <c r="Q40" s="199"/>
-      <c r="R40" s="199"/>
-      <c r="S40" s="199"/>
+      <c r="P40" s="243"/>
+      <c r="Q40" s="243"/>
+      <c r="R40" s="243"/>
+      <c r="S40" s="243"/>
       <c r="U40" s="152"/>
       <c r="V40" s="152"/>
-      <c r="W40" s="297"/>
-      <c r="X40" s="297"/>
-      <c r="Y40" s="312"/>
-      <c r="Z40" s="312"/>
+      <c r="W40" s="152"/>
+      <c r="X40" s="152"/>
+      <c r="Y40" s="310"/>
+      <c r="Z40" s="310"/>
     </row>
     <row r="41" spans="2:35" ht="18.75" customHeight="1">
-      <c r="B41" s="208"/>
-      <c r="D41" s="208"/>
-      <c r="F41" s="200"/>
-      <c r="G41" s="200"/>
-      <c r="H41" s="200"/>
-      <c r="L41" s="199"/>
-      <c r="M41" s="199"/>
-      <c r="N41" s="199"/>
+      <c r="B41" s="229"/>
+      <c r="D41" s="229"/>
+      <c r="F41" s="232"/>
+      <c r="G41" s="232"/>
+      <c r="H41" s="232"/>
+      <c r="L41" s="243"/>
+      <c r="M41" s="243"/>
+      <c r="N41" s="243"/>
       <c r="O41" s="153"/>
-      <c r="P41" s="199"/>
-      <c r="Q41" s="199"/>
-      <c r="R41" s="199"/>
-      <c r="S41" s="199"/>
-      <c r="T41" s="203" t="s">
+      <c r="P41" s="243"/>
+      <c r="Q41" s="243"/>
+      <c r="R41" s="243"/>
+      <c r="S41" s="243"/>
+      <c r="T41" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="U41" s="279" t="s">
+      <c r="U41" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="V41" s="280"/>
-      <c r="W41" s="304"/>
-      <c r="X41" s="305"/>
+      <c r="V41" s="199"/>
+      <c r="W41" s="219"/>
+      <c r="X41" s="220"/>
       <c r="Y41" s="151"/>
       <c r="Z41" s="151"/>
     </row>
     <row r="42" spans="2:35">
-      <c r="B42" s="208"/>
-      <c r="D42" s="208"/>
-      <c r="F42" s="200"/>
-      <c r="G42" s="200"/>
-      <c r="H42" s="200"/>
-      <c r="L42" s="199"/>
-      <c r="M42" s="199"/>
-      <c r="N42" s="199"/>
-      <c r="P42" s="199"/>
-      <c r="Q42" s="199"/>
-      <c r="R42" s="199"/>
-      <c r="S42" s="199"/>
-      <c r="T42" s="203"/>
-      <c r="U42" s="281"/>
-      <c r="V42" s="282"/>
-      <c r="W42" s="306"/>
-      <c r="X42" s="307"/>
+      <c r="B42" s="229"/>
+      <c r="D42" s="229"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
+      <c r="L42" s="243"/>
+      <c r="M42" s="243"/>
+      <c r="N42" s="243"/>
+      <c r="P42" s="243"/>
+      <c r="Q42" s="243"/>
+      <c r="R42" s="243"/>
+      <c r="S42" s="243"/>
+      <c r="T42" s="249"/>
+      <c r="U42" s="200"/>
+      <c r="V42" s="201"/>
+      <c r="W42" s="221"/>
+      <c r="X42" s="222"/>
       <c r="Y42" s="151"/>
       <c r="Z42" s="151"/>
     </row>
     <row r="43" spans="2:35">
-      <c r="B43" s="208"/>
-      <c r="D43" s="208"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="200"/>
-      <c r="L43" s="199"/>
-      <c r="M43" s="199"/>
-      <c r="N43" s="199"/>
-      <c r="P43" s="199"/>
-      <c r="Q43" s="199"/>
-      <c r="R43" s="199"/>
-      <c r="S43" s="199"/>
-      <c r="T43" s="203"/>
-      <c r="U43" s="283"/>
-      <c r="V43" s="284"/>
-      <c r="W43" s="308"/>
-      <c r="X43" s="309"/>
+      <c r="B43" s="229"/>
+      <c r="D43" s="229"/>
+      <c r="F43" s="232"/>
+      <c r="G43" s="232"/>
+      <c r="H43" s="232"/>
+      <c r="L43" s="243"/>
+      <c r="M43" s="243"/>
+      <c r="N43" s="243"/>
+      <c r="P43" s="243"/>
+      <c r="Q43" s="243"/>
+      <c r="R43" s="243"/>
+      <c r="S43" s="243"/>
+      <c r="T43" s="249"/>
+      <c r="U43" s="202"/>
+      <c r="V43" s="203"/>
+      <c r="W43" s="223"/>
+      <c r="X43" s="224"/>
       <c r="Y43" s="151"/>
       <c r="Z43" s="151"/>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="198" t="s">
+      <c r="B49" s="242" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="198"/>
-      <c r="D49" s="198"/>
-      <c r="E49" s="198"/>
-      <c r="F49" s="198"/>
+      <c r="C49" s="242"/>
+      <c r="D49" s="242"/>
+      <c r="E49" s="242"/>
+      <c r="F49" s="242"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="154"/>
-      <c r="C50" s="313" t="s">
+      <c r="C50" s="311" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="313"/>
-      <c r="E50" s="313"/>
-      <c r="F50" s="313"/>
+      <c r="D50" s="311"/>
+      <c r="E50" s="311"/>
+      <c r="F50" s="311"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="155"/>
-      <c r="C51" s="313" t="s">
+      <c r="C51" s="311" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="313"/>
-      <c r="E51" s="313"/>
-      <c r="F51" s="313"/>
+      <c r="D51" s="311"/>
+      <c r="E51" s="311"/>
+      <c r="F51" s="311"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="156"/>
-      <c r="C52" s="313" t="s">
+      <c r="C52" s="311" t="s">
         <v>35</v>
       </c>
-      <c r="D52" s="313"/>
-      <c r="E52" s="313"/>
-      <c r="F52" s="313"/>
+      <c r="D52" s="311"/>
+      <c r="E52" s="311"/>
+      <c r="F52" s="311"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="157"/>
-      <c r="C53" s="313" t="s">
+      <c r="C53" s="311" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="313"/>
-      <c r="E53" s="313"/>
-      <c r="F53" s="313"/>
+      <c r="D53" s="311"/>
+      <c r="E53" s="311"/>
+      <c r="F53" s="311"/>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="158"/>
-      <c r="C54" s="313" t="s">
+      <c r="C54" s="311" t="s">
         <v>37</v>
       </c>
-      <c r="D54" s="313"/>
-      <c r="E54" s="313"/>
-      <c r="F54" s="313"/>
+      <c r="D54" s="311"/>
+      <c r="E54" s="311"/>
+      <c r="F54" s="311"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="159" t="s">
@@ -6615,18 +6613,46 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="X20:Y22"/>
-    <mergeCell ref="X24:Y26"/>
-    <mergeCell ref="U20:V26"/>
-    <mergeCell ref="W20:W22"/>
-    <mergeCell ref="W24:W26"/>
-    <mergeCell ref="U37:V39"/>
-    <mergeCell ref="W37:X39"/>
-    <mergeCell ref="U41:V43"/>
-    <mergeCell ref="W41:X43"/>
-    <mergeCell ref="P20:S26"/>
-    <mergeCell ref="T20:T22"/>
-    <mergeCell ref="T24:T26"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AB14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:V14"/>
+    <mergeCell ref="T41:T43"/>
+    <mergeCell ref="T37:T39"/>
+    <mergeCell ref="X3:Y4"/>
+    <mergeCell ref="P13:S14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="X13:Y14"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="V10:V11"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="P37:S43"/>
+    <mergeCell ref="L37:N43"/>
+    <mergeCell ref="F13:H43"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="O20:O26"/>
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L5:N11"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:H4"/>
+    <mergeCell ref="L3:N4"/>
+    <mergeCell ref="B5:B43"/>
+    <mergeCell ref="AI16:AI17"/>
+    <mergeCell ref="AH34:AI34"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="AA3:AB4"/>
+    <mergeCell ref="P3:S4"/>
+    <mergeCell ref="U3:V4"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="F9:H11"/>
+    <mergeCell ref="F5:H7"/>
+    <mergeCell ref="P17:S18"/>
     <mergeCell ref="C53:F53"/>
     <mergeCell ref="C54:F54"/>
     <mergeCell ref="L28:N29"/>
@@ -6643,46 +6669,18 @@
     <mergeCell ref="L20:N26"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="F9:H11"/>
-    <mergeCell ref="F5:H7"/>
-    <mergeCell ref="P17:S18"/>
-    <mergeCell ref="A1:AO1"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L5:N11"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:H4"/>
-    <mergeCell ref="L3:N4"/>
-    <mergeCell ref="B5:B43"/>
-    <mergeCell ref="AI16:AI17"/>
-    <mergeCell ref="AH34:AI34"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="P37:S43"/>
-    <mergeCell ref="L37:N43"/>
-    <mergeCell ref="F13:H43"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="O20:O26"/>
-    <mergeCell ref="AA3:AB4"/>
-    <mergeCell ref="P3:S4"/>
-    <mergeCell ref="U3:V4"/>
-    <mergeCell ref="X3:Y4"/>
-    <mergeCell ref="P13:S14"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="X13:Y14"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="V10:V11"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AB14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:V14"/>
-    <mergeCell ref="T41:T43"/>
-    <mergeCell ref="T37:T39"/>
+    <mergeCell ref="U37:V39"/>
+    <mergeCell ref="W37:X39"/>
+    <mergeCell ref="U41:V43"/>
+    <mergeCell ref="W41:X43"/>
+    <mergeCell ref="P20:S26"/>
+    <mergeCell ref="T20:T22"/>
+    <mergeCell ref="T24:T26"/>
+    <mergeCell ref="X20:Y22"/>
+    <mergeCell ref="X24:Y26"/>
+    <mergeCell ref="U20:V26"/>
+    <mergeCell ref="W20:W22"/>
+    <mergeCell ref="W24:W26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6764,8 +6762,8 @@
       </c>
       <c r="B6" s="69"/>
       <c r="C6" s="69"/>
-      <c r="D6" s="253"/>
-      <c r="E6" s="253"/>
+      <c r="D6" s="290"/>
+      <c r="E6" s="290"/>
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -6778,10 +6776,10 @@
       <c r="C7" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="D7" s="254" t="s">
+      <c r="D7" s="291" t="s">
         <v>231</v>
       </c>
-      <c r="E7" s="255"/>
+      <c r="E7" s="292"/>
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -6794,10 +6792,10 @@
       <c r="C8" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="251" t="s">
+      <c r="D8" s="288" t="s">
         <v>411</v>
       </c>
-      <c r="E8" s="252"/>
+      <c r="E8" s="289"/>
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -6810,10 +6808,10 @@
       <c r="C9" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="251" t="s">
+      <c r="D9" s="288" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="252"/>
+      <c r="E9" s="289"/>
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -6826,10 +6824,10 @@
       <c r="C10" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="251" t="s">
+      <c r="D10" s="288" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="252"/>
+      <c r="E10" s="289"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="10" t="s">
@@ -6841,10 +6839,10 @@
       <c r="C11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="251" t="s">
+      <c r="D11" s="288" t="s">
         <v>155</v>
       </c>
-      <c r="E11" s="252"/>
+      <c r="E11" s="289"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="10" t="s">
@@ -6856,10 +6854,10 @@
       <c r="C12" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="251" t="s">
+      <c r="D12" s="288" t="s">
         <v>413</v>
       </c>
-      <c r="E12" s="252"/>
+      <c r="E12" s="289"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="10" t="s">
@@ -6871,10 +6869,10 @@
       <c r="C13" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="251" t="s">
+      <c r="D13" s="288" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="252"/>
+      <c r="E13" s="289"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="10" t="s">
@@ -6886,10 +6884,10 @@
       <c r="C14" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="251" t="s">
+      <c r="D14" s="288" t="s">
         <v>415</v>
       </c>
-      <c r="E14" s="252"/>
+      <c r="E14" s="289"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -7139,13 +7137,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="293" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="257"/>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
+      <c r="B1" s="294"/>
+      <c r="C1" s="294"/>
+      <c r="D1" s="294"/>
+      <c r="E1" s="294"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="72" t="s">
@@ -7187,13 +7185,13 @@
       <c r="E4" s="74"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="257" t="s">
+      <c r="A5" s="294" t="s">
         <v>422</v>
       </c>
-      <c r="B5" s="257"/>
-      <c r="C5" s="257"/>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
+      <c r="B5" s="294"/>
+      <c r="C5" s="294"/>
+      <c r="D5" s="294"/>
+      <c r="E5" s="294"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="72" t="s">
@@ -7326,14 +7324,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="295" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="259"/>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
+      <c r="B1" s="296"/>
+      <c r="C1" s="296"/>
+      <c r="D1" s="296"/>
+      <c r="E1" s="296"/>
+      <c r="F1" s="296"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="77" t="s">
@@ -7342,10 +7340,10 @@
       <c r="B2" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="297" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="261"/>
+      <c r="D2" s="298"/>
       <c r="E2" s="77" t="s">
         <v>84</v>
       </c>
@@ -7360,8 +7358,8 @@
       <c r="B3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="262"/>
-      <c r="D3" s="263"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="300"/>
       <c r="E3" s="79" t="s">
         <v>87</v>
       </c>
@@ -7378,13 +7376,13 @@
       <c r="F4" s="80"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="259" t="s">
+      <c r="A5" s="296" t="s">
         <v>431</v>
       </c>
-      <c r="B5" s="259"/>
-      <c r="C5" s="259"/>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
+      <c r="B5" s="296"/>
+      <c r="C5" s="296"/>
+      <c r="D5" s="296"/>
+      <c r="E5" s="296"/>
       <c r="F5" s="81"/>
     </row>
     <row r="6" spans="1:6">
@@ -8644,14 +8642,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="264" t="s">
+      <c r="A1" s="301" t="s">
         <v>496</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
+      <c r="B1" s="302"/>
+      <c r="C1" s="302"/>
+      <c r="D1" s="302"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="71" t="s">
@@ -8660,10 +8658,10 @@
       <c r="B2" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="265" t="s">
+      <c r="C2" s="302" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="265"/>
+      <c r="D2" s="302"/>
       <c r="E2" s="71" t="s">
         <v>84</v>
       </c>
@@ -8680,13 +8678,13 @@
       <c r="F3" s="86"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="265" t="s">
+      <c r="A4" s="302" t="s">
         <v>497</v>
       </c>
-      <c r="B4" s="265"/>
-      <c r="C4" s="265"/>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
+      <c r="B4" s="302"/>
+      <c r="C4" s="302"/>
+      <c r="D4" s="302"/>
+      <c r="E4" s="302"/>
       <c r="F4" s="87"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -9937,13 +9935,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="266" t="s">
+      <c r="A1" s="303" t="s">
         <v>499</v>
       </c>
-      <c r="B1" s="267"/>
-      <c r="C1" s="267"/>
-      <c r="D1" s="267"/>
-      <c r="E1" s="267"/>
+      <c r="B1" s="304"/>
+      <c r="C1" s="304"/>
+      <c r="D1" s="304"/>
+      <c r="E1" s="304"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="92" t="s">
@@ -9978,13 +9976,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="268" t="s">
+      <c r="A4" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B4" s="269"/>
-      <c r="C4" s="269"/>
-      <c r="D4" s="269"/>
-      <c r="E4" s="270"/>
+      <c r="B4" s="306"/>
+      <c r="C4" s="306"/>
+      <c r="D4" s="306"/>
+      <c r="E4" s="307"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="92" t="s">
@@ -10100,13 +10098,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="271" t="s">
+      <c r="A1" s="308" t="s">
         <v>504</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
+      <c r="B1" s="309"/>
+      <c r="C1" s="309"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="96" t="s">
@@ -10133,13 +10131,13 @@
       <c r="E3" s="97"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="265" t="s">
+      <c r="A5" s="302" t="s">
         <v>505</v>
       </c>
-      <c r="B5" s="265"/>
-      <c r="C5" s="265"/>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
+      <c r="B5" s="302"/>
+      <c r="C5" s="302"/>
+      <c r="D5" s="302"/>
+      <c r="E5" s="302"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="71" t="s">
@@ -10571,25 +10569,25 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" ht="409.6">
       <c r="A14" t="s">
         <v>67</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" ht="409.6">
       <c r="A15" t="s">
         <v>67</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -10622,7 +10620,7 @@
       <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="311" t="s">
+      <c r="D18" s="107" t="s">
         <v>72</v>
       </c>
     </row>
@@ -10724,16 +10722,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="250" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="314"/>
+      <c r="B1" s="251"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
+      <c r="G1" s="252"/>
+      <c r="H1" s="312"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="104" t="s">
@@ -10748,12 +10746,12 @@
       <c r="D2" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="215" t="s">
+      <c r="E2" s="251" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="217"/>
-      <c r="H2" s="314"/>
+      <c r="F2" s="251"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="312"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="101">
@@ -10768,10 +10766,10 @@
       <c r="D3" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="219"/>
-      <c r="H3" s="314"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="312"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="101">
@@ -10786,24 +10784,24 @@
       <c r="D4" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="254" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219"/>
-      <c r="H4" s="314"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="312"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="220" t="s">
+      <c r="A5" s="256" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="221"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="221"/>
-      <c r="E5" s="221"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="314"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="312"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="104" t="s">
@@ -10827,7 +10825,7 @@
       <c r="G6" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="314"/>
+      <c r="H6" s="312"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="101">
@@ -10851,7 +10849,7 @@
       <c r="G7" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="314"/>
+      <c r="H7" s="312"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="101">
@@ -10875,7 +10873,7 @@
       <c r="G8" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="314"/>
+      <c r="H8" s="312"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="101">
@@ -10899,7 +10897,7 @@
       <c r="G9" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="314"/>
+      <c r="H9" s="312"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="101">
@@ -10923,7 +10921,7 @@
       <c r="G10" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="314"/>
+      <c r="H10" s="312"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="101">
@@ -10947,7 +10945,7 @@
       <c r="G11" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H11" s="314"/>
+      <c r="H11" s="312"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="101">
@@ -10971,7 +10969,7 @@
       <c r="G12" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="314"/>
+      <c r="H12" s="312"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="101">
@@ -10995,7 +10993,7 @@
       <c r="G13" s="102" t="s">
         <v>118</v>
       </c>
-      <c r="H13" s="314"/>
+      <c r="H13" s="312"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="101">
@@ -11019,7 +11017,7 @@
       <c r="G14" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="314"/>
+      <c r="H14" s="312"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="101">
@@ -11043,7 +11041,7 @@
       <c r="G15" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="314"/>
+      <c r="H15" s="312"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="101">
@@ -11067,7 +11065,7 @@
       <c r="G16" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="314"/>
+      <c r="H16" s="312"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="101">
@@ -11091,7 +11089,7 @@
       <c r="G17" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H17" s="314"/>
+      <c r="H17" s="312"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="101">
@@ -11115,7 +11113,7 @@
       <c r="G18" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="314"/>
+      <c r="H18" s="312"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="101">
@@ -11139,7 +11137,7 @@
       <c r="G19" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="314"/>
+      <c r="H19" s="312"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="101">
@@ -11163,7 +11161,7 @@
       <c r="G20" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="314"/>
+      <c r="H20" s="312"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="101">
@@ -11187,7 +11185,7 @@
       <c r="G21" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="314"/>
+      <c r="H21" s="312"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="101">
@@ -11211,7 +11209,7 @@
       <c r="G22" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H22" s="314"/>
+      <c r="H22" s="312"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="101">
@@ -11235,7 +11233,7 @@
       <c r="G23" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H23" s="314"/>
+      <c r="H23" s="312"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="101">
@@ -11259,7 +11257,7 @@
       <c r="G24" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="314"/>
+      <c r="H24" s="312"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="101">
@@ -11283,7 +11281,7 @@
       <c r="G25" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="314"/>
+      <c r="H25" s="312"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="101">
@@ -11307,7 +11305,7 @@
       <c r="G26" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H26" s="314"/>
+      <c r="H26" s="312"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="101">
@@ -11331,7 +11329,7 @@
       <c r="G27" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="314"/>
+      <c r="H27" s="312"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="101">
@@ -11355,7 +11353,7 @@
       <c r="G28" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="314"/>
+      <c r="H28" s="312"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="101">
@@ -11379,7 +11377,7 @@
       <c r="G29" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H29" s="314"/>
+      <c r="H29" s="312"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="101">
@@ -11403,7 +11401,7 @@
       <c r="G30" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H30" s="314"/>
+      <c r="H30" s="312"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="101">
@@ -11427,7 +11425,7 @@
       <c r="G31" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H31" s="314"/>
+      <c r="H31" s="312"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="101">
@@ -11451,7 +11449,7 @@
       <c r="G32" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="314"/>
+      <c r="H32" s="312"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="101">
@@ -11475,7 +11473,7 @@
       <c r="G33" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="314"/>
+      <c r="H33" s="312"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="101">
@@ -11499,7 +11497,7 @@
       <c r="G34" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H34" s="314"/>
+      <c r="H34" s="312"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="101">
@@ -11523,7 +11521,7 @@
       <c r="G35" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H35" s="314"/>
+      <c r="H35" s="312"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="101">
@@ -11547,7 +11545,7 @@
       <c r="G36" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H36" s="314"/>
+      <c r="H36" s="312"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="101">
@@ -11571,7 +11569,7 @@
       <c r="G37" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H37" s="314"/>
+      <c r="H37" s="312"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="101">
@@ -11595,7 +11593,7 @@
       <c r="G38" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H38" s="314"/>
+      <c r="H38" s="312"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="101">
@@ -11619,7 +11617,7 @@
       <c r="G39" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H39" s="314"/>
+      <c r="H39" s="312"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="101">
@@ -11643,7 +11641,7 @@
       <c r="G40" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H40" s="314"/>
+      <c r="H40" s="312"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="101">
@@ -11667,7 +11665,7 @@
       <c r="G41" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="314"/>
+      <c r="H41" s="312"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="101">
@@ -11691,7 +11689,7 @@
       <c r="G42" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H42" s="314"/>
+      <c r="H42" s="312"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="101">
@@ -11715,7 +11713,7 @@
       <c r="G43" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H43" s="314"/>
+      <c r="H43" s="312"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="101">
@@ -11739,7 +11737,7 @@
       <c r="G44" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H44" s="314"/>
+      <c r="H44" s="312"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="101">
@@ -11763,7 +11761,7 @@
       <c r="G45" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H45" s="314"/>
+      <c r="H45" s="312"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="101">
@@ -11787,7 +11785,7 @@
       <c r="G46" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H46" s="314"/>
+      <c r="H46" s="312"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="101">
@@ -11811,7 +11809,7 @@
       <c r="G47" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H47" s="314"/>
+      <c r="H47" s="312"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="101">
@@ -11835,7 +11833,7 @@
       <c r="G48" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H48" s="314"/>
+      <c r="H48" s="312"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="101">
@@ -11859,7 +11857,7 @@
       <c r="G49" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="314"/>
+      <c r="H49" s="312"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="101">
@@ -11883,7 +11881,7 @@
       <c r="G50" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="314"/>
+      <c r="H50" s="312"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="101">
@@ -11907,7 +11905,7 @@
       <c r="G51" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="314"/>
+      <c r="H51" s="312"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="101">
@@ -11931,7 +11929,7 @@
       <c r="G52" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H52" s="314"/>
+      <c r="H52" s="312"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="101">
@@ -11955,7 +11953,7 @@
       <c r="G53" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H53" s="314"/>
+      <c r="H53" s="312"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="101">
@@ -11979,7 +11977,7 @@
       <c r="G54" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H54" s="314"/>
+      <c r="H54" s="312"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="101">
@@ -12003,7 +12001,7 @@
       <c r="G55" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H55" s="314"/>
+      <c r="H55" s="312"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="101">
@@ -12027,7 +12025,7 @@
       <c r="G56" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H56" s="314"/>
+      <c r="H56" s="312"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="101">
@@ -12051,7 +12049,7 @@
       <c r="G57" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="314"/>
+      <c r="H57" s="312"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="145">
@@ -12075,137 +12073,137 @@
       <c r="G58" s="146" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="314"/>
+      <c r="H58" s="312"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="315">
+      <c r="A59" s="313">
         <v>53</v>
       </c>
-      <c r="B59" s="316" t="s">
+      <c r="B59" s="314" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="317" t="s">
+      <c r="C59" s="315" t="s">
         <v>211</v>
       </c>
-      <c r="D59" s="318" t="s">
+      <c r="D59" s="316" t="s">
         <v>100</v>
       </c>
-      <c r="E59" s="319" t="s">
-        <v>101</v>
-      </c>
-      <c r="F59" s="316" t="s">
+      <c r="E59" s="317" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="314" t="s">
         <v>212</v>
       </c>
-      <c r="G59" s="316" t="s">
+      <c r="G59" s="314" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="314"/>
+      <c r="H59" s="312"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="315">
+      <c r="A60" s="313">
         <v>54</v>
       </c>
-      <c r="B60" s="316" t="s">
+      <c r="B60" s="314" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="317" t="s">
+      <c r="C60" s="315" t="s">
         <v>213</v>
       </c>
-      <c r="D60" s="318" t="s">
+      <c r="D60" s="316" t="s">
         <v>100</v>
       </c>
-      <c r="E60" s="319" t="s">
-        <v>101</v>
-      </c>
-      <c r="F60" s="316" t="s">
+      <c r="E60" s="317" t="s">
+        <v>101</v>
+      </c>
+      <c r="F60" s="314" t="s">
         <v>214</v>
       </c>
-      <c r="G60" s="316" t="s">
+      <c r="G60" s="314" t="s">
         <v>103</v>
       </c>
-      <c r="H60" s="314"/>
+      <c r="H60" s="312"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="315">
+      <c r="A61" s="313">
         <v>55</v>
       </c>
-      <c r="B61" s="316" t="s">
+      <c r="B61" s="314" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="317" t="s">
+      <c r="C61" s="315" t="s">
         <v>215</v>
       </c>
-      <c r="D61" s="318" t="s">
+      <c r="D61" s="316" t="s">
         <v>100</v>
       </c>
-      <c r="E61" s="319" t="s">
-        <v>101</v>
-      </c>
-      <c r="F61" s="316" t="s">
+      <c r="E61" s="317" t="s">
+        <v>101</v>
+      </c>
+      <c r="F61" s="314" t="s">
         <v>216</v>
       </c>
-      <c r="G61" s="316" t="s">
+      <c r="G61" s="314" t="s">
         <v>103</v>
       </c>
-      <c r="H61" s="314"/>
+      <c r="H61" s="312"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="315">
+      <c r="A62" s="313">
         <v>56</v>
       </c>
-      <c r="B62" s="316" t="s">
+      <c r="B62" s="314" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="317" t="s">
+      <c r="C62" s="315" t="s">
         <v>217</v>
       </c>
-      <c r="D62" s="318" t="s">
+      <c r="D62" s="316" t="s">
         <v>133</v>
       </c>
-      <c r="E62" s="319" t="s">
-        <v>101</v>
-      </c>
-      <c r="F62" s="316" t="s">
+      <c r="E62" s="317" t="s">
+        <v>101</v>
+      </c>
+      <c r="F62" s="314" t="s">
         <v>218</v>
       </c>
-      <c r="G62" s="316" t="s">
+      <c r="G62" s="314" t="s">
         <v>103</v>
       </c>
-      <c r="H62" s="314"/>
+      <c r="H62" s="312"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="315">
+      <c r="A63" s="313">
         <v>57</v>
       </c>
-      <c r="B63" s="316" t="s">
+      <c r="B63" s="314" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="317" t="s">
+      <c r="C63" s="315" t="s">
         <v>219</v>
       </c>
-      <c r="D63" s="318" t="s">
+      <c r="D63" s="316" t="s">
         <v>100</v>
       </c>
-      <c r="E63" s="319" t="s">
-        <v>101</v>
-      </c>
-      <c r="F63" s="316" t="s">
+      <c r="E63" s="317" t="s">
+        <v>101</v>
+      </c>
+      <c r="F63" s="314" t="s">
         <v>220</v>
       </c>
-      <c r="G63" s="316" t="s">
+      <c r="G63" s="314" t="s">
         <v>103</v>
       </c>
-      <c r="H63" s="314"/>
+      <c r="H63" s="312"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="320"/>
-      <c r="B64" s="314"/>
-      <c r="C64" s="320"/>
-      <c r="D64" s="320"/>
-      <c r="E64" s="314"/>
-      <c r="F64" s="314"/>
-      <c r="G64" s="314"/>
-      <c r="H64" s="321"/>
+      <c r="A64" s="318"/>
+      <c r="B64" s="312"/>
+      <c r="C64" s="318"/>
+      <c r="D64" s="318"/>
+      <c r="E64" s="312"/>
+      <c r="F64" s="312"/>
+      <c r="G64" s="312"/>
+      <c r="H64" s="319"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12233,14 +12231,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="259" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="224"/>
-      <c r="C1" s="224"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -12250,10 +12248,10 @@
       <c r="B2" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="225" t="s">
+      <c r="C2" s="261" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="226"/>
+      <c r="D2" s="262"/>
       <c r="E2" s="51" t="s">
         <v>84</v>
       </c>
@@ -12269,10 +12267,10 @@
       <c r="B3" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="C3" s="227" t="s">
+      <c r="C3" s="263" t="s">
         <v>223</v>
       </c>
-      <c r="D3" s="228"/>
+      <c r="D3" s="264"/>
       <c r="E3" s="52" t="s">
         <v>87</v>
       </c>
@@ -12288,10 +12286,10 @@
       <c r="B4" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="227" t="s">
+      <c r="C4" s="263" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="228"/>
+      <c r="D4" s="264"/>
       <c r="E4" s="52" t="s">
         <v>90</v>
       </c>
@@ -12300,14 +12298,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="224" t="s">
+      <c r="A5" s="260" t="s">
         <v>227</v>
       </c>
-      <c r="B5" s="224"/>
-      <c r="C5" s="224"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="224"/>
+      <c r="B5" s="260"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="51" t="s">
@@ -12437,14 +12435,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="229" t="s">
+      <c r="A1" s="265" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
+      <c r="B1" s="266"/>
+      <c r="C1" s="266"/>
+      <c r="D1" s="266"/>
+      <c r="E1" s="266"/>
+      <c r="F1" s="266"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="57" t="s">
@@ -12453,10 +12451,10 @@
       <c r="B2" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="267" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="232"/>
+      <c r="D2" s="268"/>
       <c r="E2" s="57" t="s">
         <v>84</v>
       </c>
@@ -12471,10 +12469,10 @@
       <c r="B3" s="59" t="s">
         <v>244</v>
       </c>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="269" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="234"/>
+      <c r="D3" s="270"/>
       <c r="E3" s="58" t="s">
         <v>87</v>
       </c>
@@ -12487,10 +12485,10 @@
       <c r="B4" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="271" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="236"/>
+      <c r="D4" s="272"/>
       <c r="E4" s="60" t="s">
         <v>247</v>
       </c>
@@ -12499,22 +12497,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="321"/>
-      <c r="E5" s="321"/>
-      <c r="F5" s="321"/>
+      <c r="A5" s="319"/>
+      <c r="B5" s="319"/>
+      <c r="C5" s="319"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
+      <c r="F5" s="319"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="267" t="s">
         <v>249</v>
       </c>
-      <c r="B7" s="237"/>
-      <c r="C7" s="237"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="237"/>
-      <c r="F7" s="321"/>
+      <c r="B7" s="273"/>
+      <c r="C7" s="273"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="319"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="57" t="s">
@@ -12532,7 +12530,7 @@
       <c r="E8" s="57" t="s">
         <v>231</v>
       </c>
-      <c r="F8" s="321"/>
+      <c r="F8" s="319"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="62" t="s">
@@ -12550,7 +12548,7 @@
       <c r="E9" s="65" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="321"/>
+      <c r="F9" s="319"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="62" t="s">
@@ -12568,7 +12566,7 @@
       <c r="E10" s="65" t="s">
         <v>252</v>
       </c>
-      <c r="F10" s="321"/>
+      <c r="F10" s="319"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="62" t="s">
@@ -12586,7 +12584,7 @@
       <c r="E11" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="F11" s="321"/>
+      <c r="F11" s="319"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="62" t="s">
@@ -12604,7 +12602,7 @@
       <c r="E12" s="65" t="s">
         <v>258</v>
       </c>
-      <c r="F12" s="321"/>
+      <c r="F12" s="319"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="62" t="s">
@@ -12622,7 +12620,7 @@
       <c r="E13" s="65" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="321"/>
+      <c r="F13" s="319"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="62" t="s">
@@ -12640,7 +12638,7 @@
       <c r="E14" s="65" t="s">
         <v>263</v>
       </c>
-      <c r="F14" s="321"/>
+      <c r="F14" s="319"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="62" t="s">
@@ -12658,7 +12656,7 @@
       <c r="E15" s="65" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="321"/>
+      <c r="F15" s="319"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12685,13 +12683,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="276" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="242"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="278"/>
       <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6">
@@ -12792,39 +12790,39 @@
       <c r="E7" s="31"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="240" t="s">
+      <c r="A8" s="276" t="s">
         <v>275</v>
       </c>
-      <c r="B8" s="241"/>
-      <c r="C8" s="241"/>
-      <c r="D8" s="241"/>
-      <c r="E8" s="241"/>
+      <c r="B8" s="277"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="277"/>
+      <c r="E8" s="277"/>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="243" t="s">
+      <c r="A9" s="279" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="244" t="s">
+      <c r="B9" s="280" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="280" t="s">
         <v>230</v>
       </c>
-      <c r="D9" s="245" t="s">
+      <c r="D9" s="281" t="s">
         <v>231</v>
       </c>
-      <c r="E9" s="245" t="s">
+      <c r="E9" s="281" t="s">
         <v>278</v>
       </c>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="243"/>
-      <c r="B10" s="244"/>
-      <c r="C10" s="244"/>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
+      <c r="A10" s="279"/>
+      <c r="B10" s="280"/>
+      <c r="C10" s="280"/>
+      <c r="D10" s="282"/>
+      <c r="E10" s="282"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6">
@@ -13854,13 +13852,13 @@
       <c r="F67" s="7"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="238" t="s">
+      <c r="A68" s="274" t="s">
         <v>295</v>
       </c>
-      <c r="B68" s="239"/>
-      <c r="C68" s="239"/>
-      <c r="D68" s="239"/>
-      <c r="E68" s="239"/>
+      <c r="B68" s="275"/>
+      <c r="C68" s="275"/>
+      <c r="D68" s="275"/>
+      <c r="E68" s="275"/>
       <c r="F68" s="7"/>
     </row>
     <row r="69" spans="1:6">
@@ -14909,13 +14907,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="283" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="249"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="285"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="137" t="s">
@@ -14941,7 +14939,7 @@
       <c r="B3" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="310" t="s">
+      <c r="C3" s="191" t="s">
         <v>325</v>
       </c>
       <c r="D3" s="139" t="s">
@@ -14952,13 +14950,13 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="250" t="s">
+      <c r="A5" s="286" t="s">
         <v>327</v>
       </c>
-      <c r="B5" s="250"/>
-      <c r="C5" s="250"/>
-      <c r="D5" s="250"/>
-      <c r="E5" s="250"/>
+      <c r="B5" s="286"/>
+      <c r="C5" s="286"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="136" t="s">
@@ -15140,13 +15138,13 @@
       <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="191" t="s">
+      <c r="A5" s="287" t="s">
         <v>275</v>
       </c>
-      <c r="B5" s="191"/>
-      <c r="C5" s="191"/>
-      <c r="D5" s="191"/>
-      <c r="E5" s="191"/>
+      <c r="B5" s="287"/>
+      <c r="C5" s="287"/>
+      <c r="D5" s="287"/>
+      <c r="E5" s="287"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="23" t="s">
@@ -15472,14 +15470,14 @@
       <c r="G11" s="128"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
-      <c r="A12" s="191" t="s">
+      <c r="A12" s="287" t="s">
         <v>275</v>
       </c>
-      <c r="B12" s="191"/>
-      <c r="C12" s="191"/>
-      <c r="D12" s="191"/>
-      <c r="E12" s="191"/>
-      <c r="F12" s="191"/>
+      <c r="B12" s="287"/>
+      <c r="C12" s="287"/>
+      <c r="D12" s="287"/>
+      <c r="E12" s="287"/>
+      <c r="F12" s="287"/>
       <c r="G12" s="190"/>
     </row>
     <row r="13" spans="1:8" ht="27">
@@ -16008,15 +16006,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -16026,14 +16015,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>